--- a/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Triphammer_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/FingerLakes Farms/FingerLakes Farms_Triphammer_20251031.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.50</t>
+          <t>9.25</t>
         </is>
       </c>
     </row>
